--- a/sample/客の台帳.xlsx
+++ b/sample/客の台帳.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">番号</t>
   </si>
@@ -28,6 +28,12 @@
     <t xml:space="preserve">案内可</t>
   </si>
   <si>
+    <t xml:space="preserve">同意した日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同意の取り方</t>
+  </si>
+  <si>
     <t xml:space="preserve">断った日</t>
   </si>
   <si>
@@ -52,6 +58,12 @@
     <t xml:space="preserve">○</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-04-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会員申込の頁</t>
+  </si>
+  <si>
     <t xml:space="preserve">青しそと聖護院かぶ</t>
   </si>
   <si>
@@ -70,6 +82,12 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">申込書(紙)</t>
+  </si>
+  <si>
     <t xml:space="preserve">豆をまとめて</t>
   </si>
   <si>
@@ -88,7 +106,7 @@
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">**同意をもらっていない** — 作らない</t>
+    <t xml:space="preserve">**会員でない** — 作らない</t>
   </si>
   <si>
     <t xml:space="preserve">004</t>
@@ -106,10 +124,43 @@
     <t xml:space="preserve">2026-03-11</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-01-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
     <t xml:space="preserve">**断られた** — 作らない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">田中 実</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minoru@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">〒444-4444 あちらの県あちらの市2-2-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**○ だけで証跡が無い** — 作らない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中村 さくら</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sakura@example.invalid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">〒555-5555 そちらの県そちらの市3-3-3</t>
   </si>
 </sst>
 </file>
@@ -152,6 +203,115 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
@@ -161,8 +321,10 @@
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -190,97 +352,167 @@
       <c r="H1" t="s" s="1">
         <v>7</v>
       </c>
+      <c r="I1" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
+      <c r="G3" t="s">
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
